--- a/data/trans_camb/P7_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P7_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 5,01</t>
+          <t>-3,11; 4,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 3,41</t>
+          <t>-4,52; 3,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 10,26</t>
+          <t>1,17; 9,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 2,56</t>
+          <t>-7,04; 2,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 2,22</t>
+          <t>-7,69; 1,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 0,17</t>
+          <t>-10,11; 0,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 2,72</t>
+          <t>-3,95; 2,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 1,32</t>
+          <t>-4,92; 1,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 4,08</t>
+          <t>-3,1; 3,93</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 32,19</t>
+          <t>-16,94; 31,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,42; 21,72</t>
+          <t>-23,17; 21,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,29; 66,87</t>
+          <t>6,43; 61,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,76; 9,29</t>
+          <t>-21,87; 8,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,96; 7,94</t>
+          <t>-23,73; 7,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,68; -0,09</t>
+          <t>-32,01; -0,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 12,03</t>
+          <t>-15,86; 12,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,93; 6,14</t>
+          <t>-19,53; 7,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 18,35</t>
+          <t>-12,36; 17,35</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 5,28</t>
+          <t>-1,35; 5,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 3,6</t>
+          <t>-3,04; 3,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 0,56</t>
+          <t>-10,58; 0,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,04; -0,46</t>
+          <t>-8,43; 0,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,02; -3,59</t>
+          <t>-11,69; -3,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,76; -3,46</t>
+          <t>-10,87; -3,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 1,58</t>
+          <t>-3,96; 1,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,3; -0,89</t>
+          <t>-6,24; -1,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,37; -2,93</t>
+          <t>-13,54; -2,99</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 38,58</t>
+          <t>-8,22; 41,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,76; 25,58</t>
+          <t>-17,47; 25,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-60,27; 2,87</t>
+          <t>-62,64; 2,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-26,84; -1,75</t>
+          <t>-24,97; 0,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,59; -11,9</t>
+          <t>-34,51; -11,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,59; -11,66</t>
+          <t>-32,13; -10,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,86; 7,13</t>
+          <t>-16,07; 5,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,44; -4,12</t>
+          <t>-25,31; -5,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-51,28; -13,31</t>
+          <t>-53,65; -12,99</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 4,33</t>
+          <t>-3,24; 4,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 3,5</t>
+          <t>-3,85; 3,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 4,01</t>
+          <t>-4,27; 3,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 6,13</t>
+          <t>-3,34; 6,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 0,69</t>
+          <t>-8,99; 0,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,13; -4,51</t>
+          <t>-20,02; -4,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 4,21</t>
+          <t>-1,92; 4,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 0,75</t>
+          <t>-5,02; 0,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,76; -2,01</t>
+          <t>-10,72; -1,65</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-20,15; 29,55</t>
+          <t>-18,51; 35,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,39; 25,48</t>
+          <t>-21,63; 30,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-24,06; 29,3</t>
+          <t>-22,52; 28,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-11,41; 25,57</t>
+          <t>-11,67; 25,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,81; 2,94</t>
+          <t>-31,44; 0,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-67,19; -17,31</t>
+          <t>-72,89; -17,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 21,67</t>
+          <t>-8,54; 22,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,51; 3,98</t>
+          <t>-22,42; 4,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-51,26; -10,3</t>
+          <t>-48,33; -8,38</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 3,88</t>
+          <t>-2,91; 3,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 3,87</t>
+          <t>-2,75; 3,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,18; 7,85</t>
+          <t>1,28; 7,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 2,33</t>
+          <t>-5,57; 2,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 0,81</t>
+          <t>-7,11; 0,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 0,44</t>
+          <t>-8,54; 0,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 1,87</t>
+          <t>-3,17; 1,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 1,2</t>
+          <t>-3,89; 1,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 3,05</t>
+          <t>-2,76; 2,71</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-17,09; 29,88</t>
+          <t>-18,22; 29,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,9; 29,74</t>
+          <t>-16,35; 29,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,27; 61,21</t>
+          <t>8,0; 58,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 9,49</t>
+          <t>-20,39; 9,05</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-26,21; 3,04</t>
+          <t>-25,45; 2,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-29,49; 1,22</t>
+          <t>-31,66; 1,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-14,79; 9,35</t>
+          <t>-14,59; 9,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-19,1; 6,42</t>
+          <t>-17,62; 5,68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 15,52</t>
+          <t>-12,39; 13,56</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 2,9</t>
+          <t>-0,74; 2,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 1,82</t>
+          <t>-1,8; 1,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 2,91</t>
+          <t>-3,03; 3,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 0,26</t>
+          <t>-4,18; 0,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,81; -2,63</t>
+          <t>-6,76; -2,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,94; -4,09</t>
+          <t>-10,7; -4,01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,84</t>
+          <t>-1,84; 1,03</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,87; -1,03</t>
+          <t>-3,66; -0,87</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,39; -1,11</t>
+          <t>-5,86; -1,23</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 19,81</t>
+          <t>-4,53; 19,69</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 12,22</t>
+          <t>-10,81; 12,42</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 19,1</t>
+          <t>-18,01; 19,7</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 1,07</t>
+          <t>-14,19; 1,13</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-23,1; -9,44</t>
+          <t>-22,65; -9,4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-37,41; -14,8</t>
+          <t>-37,15; -14,92</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 3,91</t>
+          <t>-8,01; 4,81</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-16,73; -4,85</t>
+          <t>-16,11; -4,22</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-23,76; -4,93</t>
+          <t>-25,64; -5,73</t>
         </is>
       </c>
     </row>
